--- a/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-organization.xlsx
+++ b/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:14:26+00:00</t>
+    <t>2026-10-14T13:25:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -510,7 +510,7 @@
     <t>Gesundheitsdiensteanbieter-OID (GDA-OID)</t>
   </si>
   <si>
-    <t>The OID of the healthcare service provider (Gesundheitsdiensteanbieter, GDA) as registered in the Austrian GDA-Index, maintained by the Federal Ministry of Health (Bundesministerium für Gesundheit).</t>
+    <t>The OID of the healthcare service provider (Gesundheitsdiensteanbieter, GDA) as registered in the Austrian GDA-Index. The OID is assigned by the Federal Ministry of Health (Bundesministerium für Gesundheit).</t>
   </si>
   <si>
     <t>Organization.identifier:GDA-OID.id</t>
@@ -630,7 +630,7 @@
     <t>Organization.identifier.system</t>
   </si>
   <si>
-    <t>A Gesundheitsdiensteanbieter (GDA) in Austria is represented via an URI (OID)</t>
+    <t>A Gesundheitsdiensteanbieter (GDA) in Austria is represented via a URI (OID)</t>
   </si>
   <si>
     <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
@@ -991,7 +991,7 @@
     <t>Krankenanstaltennummer (KA-Nr)</t>
   </si>
   <si>
-    <t>The hospital identification number (Krankenanstaltennummer, KA-Nr) of the organization according to the Austrian hospital register (Krankenanstaltenkataster), assigned by the Federal Ministry of Health (Bundesministerium für Gesundheit). Virtual KA-Nrs are suffixed with '+' (e.g. 'K101+').</t>
+    <t>The hospital identification number (Krankenanstaltennummer, KA-Nr) of the organization according to the Austrian hospital register (Krankenanstaltenkataster), assigned by the Federal Ministry of Health (Österreichisches Bundesministerium für Gesundheit). Virtual KA-Nrs are suffixed with '+' (e.g. 'K101+').</t>
   </si>
   <si>
     <t>Organization.identifier:KANR.id</t>
@@ -1018,7 +1018,7 @@
     <t>Organization.identifier:KANR.value</t>
   </si>
   <si>
-    <t>Krankenanstaltennummer according to Krankenanstaltenkataster. Virtual KANRs are suffixed with '+' (e.g. 'K101+')</t>
+    <t>Krankenanstaltennummer according to Krankenanstaltenkataster. Virtual KA-Nrs are suffixed with '+' (e.g. 'K101+')</t>
   </si>
   <si>
     <t>Organization.identifier:KANR.period</t>

--- a/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-organization.xlsx
+++ b/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T13:25:21+00:00</t>
+    <t>2026-10-19T13:57:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3613,10 +3613,10 @@
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S17" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="S17" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>203</v>
@@ -4635,10 +4635,10 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S26" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="S26" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>21</v>
@@ -5325,10 +5325,10 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S32" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="S32" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>203</v>
@@ -6347,10 +6347,10 @@
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S41" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="S41" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>21</v>
@@ -7037,10 +7037,10 @@
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S47" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T47" t="s" s="2">
         <v>203</v>
@@ -8059,10 +8059,10 @@
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S56" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>21</v>
@@ -8749,10 +8749,10 @@
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S62" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T62" t="s" s="2">
         <v>203</v>
@@ -9771,10 +9771,10 @@
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S71" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T71" t="s" s="2">
         <v>21</v>

--- a/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-organization.xlsx
+++ b/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T13:57:06+00:00</t>
+    <t>2026-10-19T15:00:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-organization.xlsx
+++ b/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:00:46+00:00</t>
+    <t>2026-10-20T05:56:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
